--- a/data-source.xlsx
+++ b/data-source.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="12920"/>
+    <workbookView windowHeight="17020"/>
   </bookViews>
   <sheets>
     <sheet name="Raw Data Report" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="82">
   <si>
     <t>date</t>
   </si>
@@ -264,6 +264,29 @@
   </si>
   <si>
     <t>BA608-包7-kkluv-GG-0517</t>
+  </si>
+  <si>
+    <r>
+      <t>BA608-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
+      <t>包</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2-kkluv-GG-0514111xxx</t>
+    </r>
   </si>
   <si>
     <t>23837397655</t>
@@ -332,16 +355,16 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10.5"/>
+      <color rgb="FF3C4043"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FF3C4043"/>
-      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1022,12 +1045,36 @@
     <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1037,33 +1084,15 @@
     <xf numFmtId="2" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1072,12 +1101,6 @@
     </xf>
     <xf numFmtId="2" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1663,10 +1686,10 @@
       <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="12" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="10" t="s">
@@ -1684,49 +1707,49 @@
       <c r="K1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="20" t="s">
+      <c r="L1" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="24" t="s">
+      <c r="M1" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="24" t="s">
+      <c r="N1" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="25" t="s">
+      <c r="O1" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="25" t="s">
+      <c r="P1" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="25" t="s">
+      <c r="Q1" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="25" t="s">
+      <c r="R1" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="25" t="s">
+      <c r="S1" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="25" t="s">
+      <c r="T1" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="29" t="s">
+      <c r="U1" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="29" t="s">
+      <c r="V1" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="25" t="s">
+      <c r="W1" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="30" t="s">
+      <c r="X1" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="13" t="s">
+      <c r="Y1" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="13" t="s">
+      <c r="Z1" s="18" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1734,19 +1757,19 @@
       <c r="A2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="18" t="s">
         <v>26</v>
       </c>
       <c r="D2" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="12" t="s">
         <v>29</v>
       </c>
       <c r="G2" s="10" t="s">
@@ -1764,192 +1787,192 @@
       <c r="K2" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="L2" s="20" t="s">
+      <c r="L2" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="24" t="s">
+      <c r="M2" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="N2" s="24" t="s">
+      <c r="N2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="25" t="s">
+      <c r="O2" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="P2" s="25" t="s">
+      <c r="P2" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="25" t="s">
+      <c r="Q2" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="R2" s="25" t="s">
+      <c r="R2" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="S2" s="25" t="s">
+      <c r="S2" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="T2" s="25" t="s">
+      <c r="T2" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="U2" s="29" t="s">
+      <c r="U2" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="V2" s="29" t="s">
+      <c r="V2" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="W2" s="25" t="s">
+      <c r="W2" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="X2" s="30" t="s">
+      <c r="X2" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="Y2" s="13" t="s">
+      <c r="Y2" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="Z2" s="13" t="s">
+      <c r="Z2" s="18" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:26">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="18" t="s">
         <v>46</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="J3" s="13" t="s">
+      <c r="J3" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="K3" s="13" t="s">
+      <c r="K3" s="18" t="s">
         <v>48</v>
       </c>
       <c r="L3" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="M3" s="25" t="s">
+      <c r="M3" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="N3" s="25" t="s">
+      <c r="N3" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="O3" s="25" t="s">
+      <c r="O3" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="P3" s="25" t="s">
+      <c r="P3" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="Q3" s="25" t="s">
+      <c r="Q3" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="R3" s="25" t="s">
+      <c r="R3" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="S3" s="25" t="s">
+      <c r="S3" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="T3" s="25" t="s">
+      <c r="T3" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="U3" s="29" t="s">
+      <c r="U3" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="V3" s="29" t="s">
+      <c r="V3" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="W3" s="25" t="s">
+      <c r="W3" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="X3" s="30" t="s">
+      <c r="X3" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="Y3" s="13" t="s">
+      <c r="Y3" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="Z3" s="13" t="s">
+      <c r="Z3" s="18" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:26">
-      <c r="A4" s="14">
+      <c r="A4" s="22">
         <v>46158</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="16">
+      <c r="D4" s="24">
         <v>235.35</v>
       </c>
-      <c r="E4" s="19">
+      <c r="E4" s="25">
         <v>45052</v>
       </c>
-      <c r="F4" s="19">
+      <c r="F4" s="25">
         <v>1491</v>
       </c>
-      <c r="G4" s="16">
+      <c r="G4" s="24">
         <v>85</v>
       </c>
-      <c r="H4" s="16">
+      <c r="H4" s="24">
         <v>15</v>
       </c>
-      <c r="I4" s="22">
+      <c r="I4" s="26">
         <v>2.77</v>
       </c>
-      <c r="J4" s="16">
+      <c r="J4" s="24">
         <v>15.69</v>
       </c>
-      <c r="K4" s="23">
+      <c r="K4" s="27">
         <v>3.31</v>
       </c>
       <c r="L4" s="21">
         <v>200</v>
       </c>
-      <c r="M4" s="26" t="s">
+      <c r="M4" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="N4" s="26" t="s">
+      <c r="N4" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="O4" s="25">
+      <c r="O4" s="15">
         <v>90.5</v>
       </c>
-      <c r="P4" s="27" t="s">
+      <c r="P4" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="Q4" s="27" t="s">
+      <c r="Q4" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="R4" s="27">
+      <c r="R4" s="29">
         <v>0</v>
       </c>
-      <c r="S4" s="28">
+      <c r="S4" s="30">
         <f>H4</f>
         <v>15</v>
       </c>
-      <c r="T4" s="28">
+      <c r="T4" s="30">
         <f>J4</f>
         <v>15.69</v>
       </c>
@@ -1976,65 +1999,65 @@
       </c>
     </row>
     <row r="5" spans="1:26">
-      <c r="A5" s="14">
+      <c r="A5" s="22">
         <v>46158</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="24">
         <v>201</v>
       </c>
-      <c r="E5" s="19">
+      <c r="E5" s="25">
         <v>90278</v>
       </c>
-      <c r="F5" s="19">
+      <c r="F5" s="25">
         <v>1444</v>
       </c>
-      <c r="G5" s="16">
+      <c r="G5" s="24">
         <v>78</v>
       </c>
-      <c r="H5" s="16">
+      <c r="H5" s="24">
         <v>12</v>
       </c>
-      <c r="I5" s="16">
+      <c r="I5" s="24">
         <v>2.58</v>
       </c>
-      <c r="J5" s="16">
+      <c r="J5" s="24">
         <v>16.75</v>
       </c>
-      <c r="K5" s="23">
+      <c r="K5" s="27">
         <v>1.6</v>
       </c>
       <c r="L5" s="21">
         <v>200</v>
       </c>
-      <c r="M5" s="26" t="s">
+      <c r="M5" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="N5" s="26" t="s">
+      <c r="N5" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="O5" s="25">
+      <c r="O5" s="15">
         <v>97.1</v>
       </c>
-      <c r="P5" s="27" t="s">
+      <c r="P5" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="Q5" s="27" t="s">
+      <c r="Q5" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="R5" s="27">
+      <c r="R5" s="29">
         <v>0</v>
       </c>
-      <c r="S5" s="28">
+      <c r="S5" s="30">
         <f>H5</f>
         <v>12</v>
       </c>
-      <c r="T5" s="28">
+      <c r="T5" s="30">
         <f t="shared" ref="T5:T12" si="0">J5</f>
         <v>16.75</v>
       </c>
@@ -2061,65 +2084,65 @@
       </c>
     </row>
     <row r="6" spans="1:26">
-      <c r="A6" s="14">
+      <c r="A6" s="22">
         <v>46158</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="24">
         <v>107.66</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="25">
         <v>10769</v>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="25">
         <v>342</v>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="24">
         <v>25</v>
       </c>
-      <c r="H6" s="16">
+      <c r="H6" s="24">
         <v>7</v>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="24">
         <v>4.31</v>
       </c>
-      <c r="J6" s="16">
+      <c r="J6" s="24">
         <v>15.38</v>
       </c>
-      <c r="K6" s="23">
+      <c r="K6" s="27">
         <v>3.18</v>
       </c>
       <c r="L6" s="21">
         <v>200</v>
       </c>
-      <c r="M6" s="26" t="s">
+      <c r="M6" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="N6" s="26" t="s">
+      <c r="N6" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="O6" s="25">
+      <c r="O6" s="15">
         <v>98.2</v>
       </c>
-      <c r="P6" s="27" t="s">
+      <c r="P6" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="Q6" s="27" t="s">
+      <c r="Q6" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="R6" s="27">
+      <c r="R6" s="29">
         <v>0</v>
       </c>
-      <c r="S6" s="28">
+      <c r="S6" s="30">
         <f t="shared" ref="S6:S12" si="4">H6</f>
         <v>7</v>
       </c>
-      <c r="T6" s="28">
+      <c r="T6" s="30">
         <f t="shared" si="0"/>
         <v>15.38</v>
       </c>
@@ -2146,65 +2169,65 @@
       </c>
     </row>
     <row r="7" spans="1:26">
-      <c r="A7" s="14">
+      <c r="A7" s="22">
         <v>46158</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="24">
         <v>182.16</v>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="25">
         <v>16152</v>
       </c>
-      <c r="F7" s="19">
+      <c r="F7" s="25">
         <v>539</v>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="24">
         <v>41</v>
       </c>
-      <c r="H7" s="16">
+      <c r="H7" s="24">
         <v>11</v>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="24">
         <v>4.44</v>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="24">
         <v>16.56</v>
       </c>
-      <c r="K7" s="23">
+      <c r="K7" s="27">
         <v>3.34</v>
       </c>
       <c r="L7" s="21">
         <v>200</v>
       </c>
-      <c r="M7" s="26" t="s">
+      <c r="M7" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="N7" s="26" t="s">
+      <c r="N7" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="O7" s="25">
+      <c r="O7" s="15">
         <v>94.3</v>
       </c>
-      <c r="P7" s="27" t="s">
+      <c r="P7" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="Q7" s="27" t="s">
+      <c r="Q7" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="R7" s="27">
+      <c r="R7" s="29">
         <v>0</v>
       </c>
-      <c r="S7" s="28">
+      <c r="S7" s="30">
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
-      <c r="T7" s="28">
+      <c r="T7" s="30">
         <f t="shared" si="0"/>
         <v>16.56</v>
       </c>
@@ -2231,65 +2254,65 @@
       </c>
     </row>
     <row r="8" spans="1:26">
-      <c r="A8" s="14">
+      <c r="A8" s="22">
         <v>46158</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="24">
         <v>259.56</v>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="25">
         <v>134569</v>
       </c>
-      <c r="F8" s="19">
+      <c r="F8" s="25">
         <v>2045</v>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="24">
         <v>90</v>
       </c>
-      <c r="H8" s="16">
+      <c r="H8" s="24">
         <v>18</v>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="24">
         <v>2.88</v>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="24">
         <v>14.42</v>
       </c>
-      <c r="K8" s="23">
+      <c r="K8" s="27">
         <v>1.52</v>
       </c>
       <c r="L8" s="21">
         <v>200</v>
       </c>
-      <c r="M8" s="26" t="s">
+      <c r="M8" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="N8" s="26" t="s">
+      <c r="N8" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="O8" s="25">
+      <c r="O8" s="15">
         <v>93.6</v>
       </c>
-      <c r="P8" s="27" t="s">
+      <c r="P8" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="Q8" s="27" t="s">
+      <c r="Q8" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="R8" s="27">
+      <c r="R8" s="29">
         <v>0</v>
       </c>
-      <c r="S8" s="28">
+      <c r="S8" s="30">
         <f t="shared" si="4"/>
         <v>18</v>
       </c>
-      <c r="T8" s="28">
+      <c r="T8" s="30">
         <f t="shared" si="0"/>
         <v>14.42</v>
       </c>
@@ -2316,65 +2339,65 @@
       </c>
     </row>
     <row r="9" spans="1:26">
-      <c r="A9" s="14">
+      <c r="A9" s="22">
         <v>46158</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="24">
         <v>1093.68</v>
       </c>
-      <c r="E9" s="19">
+      <c r="E9" s="25">
         <v>201342</v>
       </c>
-      <c r="F9" s="19">
+      <c r="F9" s="25">
         <v>6000</v>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="24">
         <v>372</v>
       </c>
-      <c r="H9" s="16">
+      <c r="H9" s="24">
         <v>72</v>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="24">
         <v>2.94</v>
       </c>
-      <c r="J9" s="16">
+      <c r="J9" s="24">
         <v>15.19</v>
       </c>
-      <c r="K9" s="23">
+      <c r="K9" s="27">
         <v>2.98</v>
       </c>
       <c r="L9" s="21">
         <v>200</v>
       </c>
-      <c r="M9" s="26" t="s">
+      <c r="M9" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="N9" s="26" t="s">
+      <c r="N9" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="O9" s="25">
+      <c r="O9" s="15">
         <v>91.8</v>
       </c>
-      <c r="P9" s="27" t="s">
+      <c r="P9" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="Q9" s="27" t="s">
+      <c r="Q9" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="R9" s="27">
+      <c r="R9" s="29">
         <v>0</v>
       </c>
-      <c r="S9" s="28">
+      <c r="S9" s="30">
         <f t="shared" si="4"/>
         <v>72</v>
       </c>
-      <c r="T9" s="28">
+      <c r="T9" s="30">
         <f t="shared" si="0"/>
         <v>15.19</v>
       </c>
@@ -2401,65 +2424,65 @@
       </c>
     </row>
     <row r="10" spans="1:26">
-      <c r="A10" s="14">
+      <c r="A10" s="22">
         <v>46158</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="24">
         <v>239.4</v>
       </c>
-      <c r="E10" s="19">
+      <c r="E10" s="25">
         <v>91381</v>
       </c>
-      <c r="F10" s="19">
+      <c r="F10" s="25">
         <v>1956</v>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="24">
         <v>88</v>
       </c>
-      <c r="H10" s="16">
+      <c r="H10" s="24">
         <v>14</v>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="24">
         <v>2.72</v>
       </c>
-      <c r="J10" s="16">
+      <c r="J10" s="24">
         <v>17.1</v>
       </c>
-      <c r="K10" s="23">
+      <c r="K10" s="27">
         <v>2.14</v>
       </c>
       <c r="L10" s="21">
         <v>200</v>
       </c>
-      <c r="M10" s="26" t="s">
+      <c r="M10" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="N10" s="26" t="s">
+      <c r="N10" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="O10" s="25">
+      <c r="O10" s="15">
         <v>96.6</v>
       </c>
-      <c r="P10" s="27" t="s">
+      <c r="P10" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="Q10" s="27" t="s">
+      <c r="Q10" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="R10" s="27">
+      <c r="R10" s="29">
         <v>0</v>
       </c>
-      <c r="S10" s="28">
+      <c r="S10" s="30">
         <f t="shared" si="4"/>
         <v>14</v>
       </c>
-      <c r="T10" s="28">
+      <c r="T10" s="30">
         <f t="shared" si="0"/>
         <v>17.1</v>
       </c>
@@ -2486,65 +2509,65 @@
       </c>
     </row>
     <row r="11" spans="1:26">
-      <c r="A11" s="14">
+      <c r="A11" s="22">
         <v>46158</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="24">
         <v>2833.57</v>
       </c>
-      <c r="E11" s="19">
+      <c r="E11" s="25">
         <v>528012</v>
       </c>
-      <c r="F11" s="19">
+      <c r="F11" s="25">
         <v>16685</v>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="24">
         <v>901</v>
       </c>
-      <c r="H11" s="16">
+      <c r="H11" s="24">
         <v>179</v>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="24">
         <v>3.14</v>
       </c>
-      <c r="J11" s="16">
+      <c r="J11" s="24">
         <v>15.83</v>
       </c>
-      <c r="K11" s="23">
+      <c r="K11" s="27">
         <v>3.16</v>
       </c>
       <c r="L11" s="21">
         <v>200</v>
       </c>
-      <c r="M11" s="26" t="s">
+      <c r="M11" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="N11" s="26" t="s">
+      <c r="N11" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="O11" s="25">
+      <c r="O11" s="15">
         <v>90.4</v>
       </c>
-      <c r="P11" s="27" t="s">
+      <c r="P11" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="Q11" s="27" t="s">
+      <c r="Q11" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="R11" s="27">
+      <c r="R11" s="29">
         <v>0</v>
       </c>
-      <c r="S11" s="28">
+      <c r="S11" s="30">
         <f t="shared" si="4"/>
         <v>179</v>
       </c>
-      <c r="T11" s="28">
+      <c r="T11" s="30">
         <f t="shared" si="0"/>
         <v>15.83</v>
       </c>
@@ -2571,65 +2594,65 @@
       </c>
     </row>
     <row r="12" spans="1:26">
-      <c r="A12" s="14">
+      <c r="A12" s="22">
         <v>46158</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="D12" s="16">
+      <c r="D12" s="24">
         <v>109.12</v>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="25">
         <v>19727</v>
       </c>
-      <c r="F12" s="19">
+      <c r="F12" s="25">
         <v>608</v>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="24">
         <v>48</v>
       </c>
-      <c r="H12" s="16">
+      <c r="H12" s="24">
         <v>8</v>
       </c>
-      <c r="I12" s="16">
+      <c r="I12" s="24">
         <v>2.27</v>
       </c>
-      <c r="J12" s="16">
+      <c r="J12" s="24">
         <v>13.64</v>
       </c>
-      <c r="K12" s="23">
+      <c r="K12" s="27">
         <v>3.08</v>
       </c>
       <c r="L12" s="21">
         <v>200</v>
       </c>
-      <c r="M12" s="26" t="s">
+      <c r="M12" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="N12" s="26" t="s">
+      <c r="N12" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="O12" s="25">
+      <c r="O12" s="15">
         <v>93.9</v>
       </c>
-      <c r="P12" s="27" t="s">
+      <c r="P12" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="Q12" s="27" t="s">
+      <c r="Q12" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="R12" s="27">
+      <c r="R12" s="29">
         <v>0</v>
       </c>
-      <c r="S12" s="28">
+      <c r="S12" s="30">
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="T12" s="28">
+      <c r="T12" s="30">
         <f t="shared" si="0"/>
         <v>13.64</v>
       </c>
@@ -2656,65 +2679,65 @@
       </c>
     </row>
     <row r="13" spans="1:26">
-      <c r="A13" s="14">
+      <c r="A13" s="22">
         <v>46159</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="16">
+      <c r="D13" s="24">
         <v>139.68</v>
       </c>
-      <c r="E13" s="19">
+      <c r="E13" s="25">
         <v>27880</v>
       </c>
-      <c r="F13" s="19">
+      <c r="F13" s="25">
         <v>655</v>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="24">
         <v>38</v>
       </c>
-      <c r="H13" s="16">
+      <c r="H13" s="24">
         <v>9</v>
       </c>
-      <c r="I13" s="16">
+      <c r="I13" s="24">
         <v>3.68</v>
       </c>
-      <c r="J13" s="16">
+      <c r="J13" s="24">
         <v>15.52</v>
       </c>
-      <c r="K13" s="23">
+      <c r="K13" s="27">
         <v>2.35</v>
       </c>
       <c r="L13" s="21">
         <v>200</v>
       </c>
-      <c r="M13" s="26" t="s">
+      <c r="M13" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="N13" s="26" t="s">
+      <c r="N13" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="O13" s="25">
+      <c r="O13" s="15">
         <v>94.7</v>
       </c>
-      <c r="P13" s="27" t="s">
+      <c r="P13" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="Q13" s="27" t="s">
+      <c r="Q13" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="R13" s="27">
+      <c r="R13" s="29">
         <v>0</v>
       </c>
-      <c r="S13" s="28">
+      <c r="S13" s="30">
         <f t="shared" ref="S13:S50" si="5">H13</f>
         <v>9</v>
       </c>
-      <c r="T13" s="28">
+      <c r="T13" s="30">
         <f t="shared" ref="T13:T31" si="6">J13</f>
         <v>15.52</v>
       </c>
@@ -2741,65 +2764,65 @@
       </c>
     </row>
     <row r="14" spans="1:26">
-      <c r="A14" s="14">
+      <c r="A14" s="22">
         <v>46159</v>
       </c>
       <c r="B14" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="16">
+      <c r="D14" s="24">
         <v>113.61</v>
       </c>
-      <c r="E14" s="19">
+      <c r="E14" s="25">
         <v>32758</v>
       </c>
-      <c r="F14" s="19">
+      <c r="F14" s="25">
         <v>753</v>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="24">
         <v>55</v>
       </c>
-      <c r="H14" s="16">
+      <c r="H14" s="24">
         <v>7</v>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="24">
         <v>2.07</v>
       </c>
-      <c r="J14" s="16">
+      <c r="J14" s="24">
         <v>16.23</v>
       </c>
-      <c r="K14" s="23">
+      <c r="K14" s="27">
         <v>2.3</v>
       </c>
       <c r="L14" s="21">
         <v>200</v>
       </c>
-      <c r="M14" s="26" t="s">
+      <c r="M14" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="N14" s="26" t="s">
+      <c r="N14" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="O14" s="25">
+      <c r="O14" s="15">
         <v>99.2</v>
       </c>
-      <c r="P14" s="27" t="s">
+      <c r="P14" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="Q14" s="27" t="s">
+      <c r="Q14" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="R14" s="27">
+      <c r="R14" s="29">
         <v>0</v>
       </c>
-      <c r="S14" s="28">
+      <c r="S14" s="30">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
-      <c r="T14" s="28">
+      <c r="T14" s="30">
         <f t="shared" si="6"/>
         <v>16.23</v>
       </c>
@@ -2826,65 +2849,65 @@
       </c>
     </row>
     <row r="15" spans="1:26">
-      <c r="A15" s="14">
+      <c r="A15" s="22">
         <v>46159</v>
       </c>
       <c r="B15" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="D15" s="16">
+      <c r="D15" s="24">
         <v>277.4</v>
       </c>
-      <c r="E15" s="19">
+      <c r="E15" s="25">
         <v>56263</v>
       </c>
-      <c r="F15" s="19">
+      <c r="F15" s="25">
         <v>1851</v>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="24">
         <v>87</v>
       </c>
-      <c r="H15" s="16">
+      <c r="H15" s="24">
         <v>20</v>
       </c>
-      <c r="I15" s="16">
+      <c r="I15" s="24">
         <v>3.19</v>
       </c>
-      <c r="J15" s="16">
+      <c r="J15" s="24">
         <v>13.87</v>
       </c>
-      <c r="K15" s="23">
+      <c r="K15" s="27">
         <v>3.29</v>
       </c>
       <c r="L15" s="21">
         <v>200</v>
       </c>
-      <c r="M15" s="26" t="s">
+      <c r="M15" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="N15" s="26" t="s">
+      <c r="N15" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="O15" s="25">
+      <c r="O15" s="15">
         <v>94.1</v>
       </c>
-      <c r="P15" s="27" t="s">
+      <c r="P15" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="Q15" s="27" t="s">
+      <c r="Q15" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="R15" s="27">
+      <c r="R15" s="29">
         <v>0</v>
       </c>
-      <c r="S15" s="28">
+      <c r="S15" s="30">
         <f t="shared" si="5"/>
         <v>20</v>
       </c>
-      <c r="T15" s="28">
+      <c r="T15" s="30">
         <f t="shared" si="6"/>
         <v>13.87</v>
       </c>
@@ -2911,65 +2934,65 @@
       </c>
     </row>
     <row r="16" spans="1:26">
-      <c r="A16" s="14">
+      <c r="A16" s="22">
         <v>46159</v>
       </c>
       <c r="B16" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="24">
         <v>110.11</v>
       </c>
-      <c r="E16" s="19">
+      <c r="E16" s="25">
         <v>24514</v>
       </c>
-      <c r="F16" s="19">
+      <c r="F16" s="25">
         <v>525</v>
       </c>
-      <c r="G16" s="16">
+      <c r="G16" s="24">
         <v>32</v>
       </c>
-      <c r="H16" s="16">
+      <c r="H16" s="24">
         <v>7</v>
       </c>
-      <c r="I16" s="16">
+      <c r="I16" s="24">
         <v>3.44</v>
       </c>
-      <c r="J16" s="16">
+      <c r="J16" s="24">
         <v>15.73</v>
       </c>
-      <c r="K16" s="23">
+      <c r="K16" s="27">
         <v>2.14</v>
       </c>
       <c r="L16" s="21">
         <v>200</v>
       </c>
-      <c r="M16" s="26" t="s">
+      <c r="M16" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="N16" s="26" t="s">
+      <c r="N16" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="O16" s="25">
+      <c r="O16" s="15">
         <v>97.7</v>
       </c>
-      <c r="P16" s="27" t="s">
+      <c r="P16" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="Q16" s="27" t="s">
+      <c r="Q16" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="R16" s="27">
+      <c r="R16" s="29">
         <v>0</v>
       </c>
-      <c r="S16" s="28">
+      <c r="S16" s="30">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
-      <c r="T16" s="28">
+      <c r="T16" s="30">
         <f t="shared" si="6"/>
         <v>15.73</v>
       </c>
@@ -2996,65 +3019,65 @@
       </c>
     </row>
     <row r="17" spans="1:26">
-      <c r="A17" s="14">
+      <c r="A17" s="22">
         <v>46159</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="D17" s="16">
+      <c r="D17" s="24">
         <v>57.04</v>
       </c>
-      <c r="E17" s="19">
+      <c r="E17" s="25">
         <v>18982</v>
       </c>
-      <c r="F17" s="19">
+      <c r="F17" s="25">
         <v>541</v>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="24">
         <v>33</v>
       </c>
-      <c r="H17" s="16">
+      <c r="H17" s="24">
         <v>4</v>
       </c>
-      <c r="I17" s="16">
+      <c r="I17" s="24">
         <v>1.73</v>
       </c>
-      <c r="J17" s="16">
+      <c r="J17" s="24">
         <v>14.26</v>
       </c>
-      <c r="K17" s="23">
+      <c r="K17" s="27">
         <v>2.85</v>
       </c>
       <c r="L17" s="21">
         <v>200</v>
       </c>
-      <c r="M17" s="26" t="s">
+      <c r="M17" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="N17" s="26" t="s">
+      <c r="N17" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="O17" s="25">
+      <c r="O17" s="15">
         <v>90.5</v>
       </c>
-      <c r="P17" s="27" t="s">
+      <c r="P17" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="Q17" s="27" t="s">
+      <c r="Q17" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="R17" s="27">
+      <c r="R17" s="29">
         <v>0</v>
       </c>
-      <c r="S17" s="28">
+      <c r="S17" s="30">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="T17" s="28">
+      <c r="T17" s="30">
         <f t="shared" si="6"/>
         <v>14.26</v>
       </c>
@@ -3081,65 +3104,65 @@
       </c>
     </row>
     <row r="18" spans="1:26">
-      <c r="A18" s="14">
+      <c r="A18" s="22">
         <v>46159</v>
       </c>
       <c r="B18" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="24">
         <v>308.6</v>
       </c>
-      <c r="E18" s="19">
+      <c r="E18" s="25">
         <v>61801</v>
       </c>
-      <c r="F18" s="19">
+      <c r="F18" s="25">
         <v>1557</v>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="24">
         <v>95</v>
       </c>
-      <c r="H18" s="16">
+      <c r="H18" s="24">
         <v>20</v>
       </c>
-      <c r="I18" s="16">
+      <c r="I18" s="24">
         <v>3.25</v>
       </c>
-      <c r="J18" s="16">
+      <c r="J18" s="24">
         <v>15.43</v>
       </c>
-      <c r="K18" s="23">
+      <c r="K18" s="27">
         <v>2.52</v>
       </c>
       <c r="L18" s="21">
         <v>200</v>
       </c>
-      <c r="M18" s="26" t="s">
+      <c r="M18" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="N18" s="26" t="s">
+      <c r="N18" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="O18" s="25">
+      <c r="O18" s="15">
         <v>97.1</v>
       </c>
-      <c r="P18" s="27" t="s">
+      <c r="P18" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="Q18" s="27" t="s">
+      <c r="Q18" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="R18" s="27">
+      <c r="R18" s="29">
         <v>0</v>
       </c>
-      <c r="S18" s="28">
+      <c r="S18" s="30">
         <f t="shared" si="5"/>
         <v>20</v>
       </c>
-      <c r="T18" s="28">
+      <c r="T18" s="30">
         <f t="shared" si="6"/>
         <v>15.43</v>
       </c>
@@ -3166,65 +3189,65 @@
       </c>
     </row>
     <row r="19" spans="1:26">
-      <c r="A19" s="14">
+      <c r="A19" s="22">
         <v>46159</v>
       </c>
       <c r="B19" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="D19" s="16">
+      <c r="D19" s="24">
         <v>628.86</v>
       </c>
-      <c r="E19" s="19">
+      <c r="E19" s="25">
         <v>340909</v>
       </c>
-      <c r="F19" s="19">
+      <c r="F19" s="25">
         <v>5591</v>
       </c>
-      <c r="G19" s="16">
+      <c r="G19" s="24">
         <v>246</v>
       </c>
-      <c r="H19" s="16">
+      <c r="H19" s="24">
         <v>47</v>
       </c>
-      <c r="I19" s="16">
+      <c r="I19" s="24">
         <v>2.56</v>
       </c>
-      <c r="J19" s="16">
+      <c r="J19" s="24">
         <v>13.38</v>
       </c>
-      <c r="K19" s="23">
+      <c r="K19" s="27">
         <v>1.64</v>
       </c>
       <c r="L19" s="21">
         <v>200</v>
       </c>
-      <c r="M19" s="26" t="s">
+      <c r="M19" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="N19" s="26" t="s">
+      <c r="N19" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="O19" s="25">
+      <c r="O19" s="15">
         <v>98.2</v>
       </c>
-      <c r="P19" s="27" t="s">
+      <c r="P19" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="Q19" s="27" t="s">
+      <c r="Q19" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="R19" s="27">
+      <c r="R19" s="29">
         <v>0</v>
       </c>
-      <c r="S19" s="28">
+      <c r="S19" s="30">
         <f t="shared" si="5"/>
         <v>47</v>
       </c>
-      <c r="T19" s="28">
+      <c r="T19" s="30">
         <f t="shared" si="6"/>
         <v>13.38</v>
       </c>
@@ -3251,65 +3274,65 @@
       </c>
     </row>
     <row r="20" spans="1:26">
-      <c r="A20" s="14">
+      <c r="A20" s="22">
         <v>46159</v>
       </c>
       <c r="B20" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="D20" s="16">
+      <c r="D20" s="24">
         <v>258.6</v>
       </c>
-      <c r="E20" s="19">
+      <c r="E20" s="25">
         <v>59626</v>
       </c>
-      <c r="F20" s="19">
+      <c r="F20" s="25">
         <v>1383</v>
       </c>
-      <c r="G20" s="16">
+      <c r="G20" s="24">
         <v>83</v>
       </c>
-      <c r="H20" s="16">
+      <c r="H20" s="24">
         <v>15</v>
       </c>
-      <c r="I20" s="16">
+      <c r="I20" s="24">
         <v>3.12</v>
       </c>
-      <c r="J20" s="16">
+      <c r="J20" s="24">
         <v>17.24</v>
       </c>
-      <c r="K20" s="23">
+      <c r="K20" s="27">
         <v>2.32</v>
       </c>
       <c r="L20" s="21">
         <v>200</v>
       </c>
-      <c r="M20" s="26" t="s">
+      <c r="M20" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="N20" s="26" t="s">
+      <c r="N20" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="O20" s="25">
+      <c r="O20" s="15">
         <v>94.3</v>
       </c>
-      <c r="P20" s="27" t="s">
+      <c r="P20" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="Q20" s="27" t="s">
+      <c r="Q20" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="R20" s="27">
+      <c r="R20" s="29">
         <v>0</v>
       </c>
-      <c r="S20" s="28">
+      <c r="S20" s="30">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="T20" s="28">
+      <c r="T20" s="30">
         <f t="shared" si="6"/>
         <v>17.24</v>
       </c>
@@ -3336,65 +3359,65 @@
       </c>
     </row>
     <row r="21" spans="1:26">
-      <c r="A21" s="14">
+      <c r="A21" s="22">
         <v>46159</v>
       </c>
       <c r="B21" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="D21" s="16">
+      <c r="D21" s="24">
         <v>2588.88</v>
       </c>
-      <c r="E21" s="19">
+      <c r="E21" s="25">
         <v>610450</v>
       </c>
-      <c r="F21" s="19">
+      <c r="F21" s="25">
         <v>16482</v>
       </c>
-      <c r="G21" s="16">
+      <c r="G21" s="24">
         <v>923</v>
       </c>
-      <c r="H21" s="16">
+      <c r="H21" s="24">
         <v>168</v>
       </c>
-      <c r="I21" s="16">
+      <c r="I21" s="24">
         <v>2.8</v>
       </c>
-      <c r="J21" s="16">
+      <c r="J21" s="24">
         <v>15.41</v>
       </c>
-      <c r="K21" s="23">
+      <c r="K21" s="27">
         <v>2.7</v>
       </c>
       <c r="L21" s="21">
         <v>200</v>
       </c>
-      <c r="M21" s="26" t="s">
+      <c r="M21" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="N21" s="26" t="s">
+      <c r="N21" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="O21" s="25">
+      <c r="O21" s="15">
         <v>93.6</v>
       </c>
-      <c r="P21" s="27" t="s">
+      <c r="P21" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="Q21" s="27" t="s">
+      <c r="Q21" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="R21" s="27">
+      <c r="R21" s="29">
         <v>0</v>
       </c>
-      <c r="S21" s="28">
+      <c r="S21" s="30">
         <f t="shared" si="5"/>
         <v>168</v>
       </c>
-      <c r="T21" s="28">
+      <c r="T21" s="30">
         <f t="shared" si="6"/>
         <v>15.41</v>
       </c>
@@ -3421,65 +3444,65 @@
       </c>
     </row>
     <row r="22" spans="1:26">
-      <c r="A22" s="14">
+      <c r="A22" s="22">
         <v>46159</v>
       </c>
       <c r="B22" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="C22" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="D22" s="16">
+      <c r="D22" s="24">
         <v>1699.4</v>
       </c>
-      <c r="E22" s="19">
+      <c r="E22" s="25">
         <v>349723</v>
       </c>
-      <c r="F22" s="19">
+      <c r="F22" s="25">
         <v>8603</v>
       </c>
-      <c r="G22" s="16">
+      <c r="G22" s="24">
         <v>542</v>
       </c>
-      <c r="H22" s="16">
+      <c r="H22" s="24">
         <v>116</v>
       </c>
-      <c r="I22" s="16">
+      <c r="I22" s="24">
         <v>3.14</v>
       </c>
-      <c r="J22" s="16">
+      <c r="J22" s="24">
         <v>14.65</v>
       </c>
-      <c r="K22" s="23">
+      <c r="K22" s="27">
         <v>2.46</v>
       </c>
       <c r="L22" s="21">
         <v>200</v>
       </c>
-      <c r="M22" s="26" t="s">
+      <c r="M22" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="N22" s="26" t="s">
+      <c r="N22" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="O22" s="25">
+      <c r="O22" s="15">
         <v>91.8</v>
       </c>
-      <c r="P22" s="27" t="s">
+      <c r="P22" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="Q22" s="27" t="s">
+      <c r="Q22" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="R22" s="27">
+      <c r="R22" s="29">
         <v>0</v>
       </c>
-      <c r="S22" s="28">
+      <c r="S22" s="30">
         <f t="shared" si="5"/>
         <v>116</v>
       </c>
-      <c r="T22" s="28">
+      <c r="T22" s="30">
         <f t="shared" si="6"/>
         <v>14.65</v>
       </c>
@@ -3506,65 +3529,65 @@
       </c>
     </row>
     <row r="23" spans="1:26">
-      <c r="A23" s="14">
+      <c r="A23" s="22">
         <v>46159</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="D23" s="16">
+      <c r="D23" s="24">
         <v>64.45</v>
       </c>
-      <c r="E23" s="19">
+      <c r="E23" s="25">
         <v>21230</v>
       </c>
-      <c r="F23" s="19">
+      <c r="F23" s="25">
         <v>391</v>
       </c>
-      <c r="G23" s="16">
+      <c r="G23" s="24">
         <v>25</v>
       </c>
-      <c r="H23" s="16">
+      <c r="H23" s="24">
         <v>5</v>
       </c>
-      <c r="I23" s="16">
+      <c r="I23" s="24">
         <v>2.58</v>
       </c>
-      <c r="J23" s="16">
+      <c r="J23" s="24">
         <v>12.89</v>
       </c>
-      <c r="K23" s="23">
+      <c r="K23" s="27">
         <v>1.84</v>
       </c>
       <c r="L23" s="21">
         <v>200</v>
       </c>
-      <c r="M23" s="26" t="s">
+      <c r="M23" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="N23" s="26" t="s">
+      <c r="N23" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="O23" s="25">
+      <c r="O23" s="15">
         <v>96.6</v>
       </c>
-      <c r="P23" s="27" t="s">
+      <c r="P23" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="Q23" s="27" t="s">
+      <c r="Q23" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="R23" s="27">
+      <c r="R23" s="29">
         <v>0</v>
       </c>
-      <c r="S23" s="28">
+      <c r="S23" s="30">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="T23" s="28">
+      <c r="T23" s="30">
         <f t="shared" si="6"/>
         <v>12.89</v>
       </c>
@@ -3591,65 +3614,65 @@
       </c>
     </row>
     <row r="24" spans="1:26">
-      <c r="A24" s="14">
+      <c r="A24" s="22">
         <v>46157</v>
       </c>
       <c r="B24" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="D24" s="16">
+      <c r="D24" s="24">
         <v>347.82</v>
       </c>
-      <c r="E24" s="19">
+      <c r="E24" s="25">
         <v>109302</v>
       </c>
-      <c r="F24" s="19">
+      <c r="F24" s="25">
         <v>2164</v>
       </c>
-      <c r="G24" s="16">
+      <c r="G24" s="24">
         <v>145</v>
       </c>
-      <c r="H24" s="16">
+      <c r="H24" s="24">
         <v>22</v>
       </c>
-      <c r="I24" s="16">
+      <c r="I24" s="24">
         <v>2.4</v>
       </c>
-      <c r="J24" s="16">
+      <c r="J24" s="24">
         <v>15.81</v>
       </c>
-      <c r="K24" s="23">
+      <c r="K24" s="27">
         <v>1.98</v>
       </c>
       <c r="L24" s="21">
         <v>200</v>
       </c>
-      <c r="M24" s="26" t="s">
+      <c r="M24" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="N24" s="26" t="s">
+      <c r="N24" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="O24" s="25">
+      <c r="O24" s="15">
         <v>90.4</v>
       </c>
-      <c r="P24" s="27" t="s">
+      <c r="P24" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="Q24" s="27" t="s">
+      <c r="Q24" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="R24" s="27">
+      <c r="R24" s="29">
         <v>0</v>
       </c>
-      <c r="S24" s="28">
+      <c r="S24" s="30">
         <f t="shared" si="5"/>
         <v>22</v>
       </c>
-      <c r="T24" s="28">
+      <c r="T24" s="30">
         <f t="shared" si="6"/>
         <v>15.81</v>
       </c>
@@ -3675,66 +3698,66 @@
         <v>56</v>
       </c>
     </row>
-    <row r="25" spans="1:26">
-      <c r="A25" s="14">
+    <row r="25" ht="17" spans="1:26">
+      <c r="A25" s="22">
         <v>46157</v>
       </c>
       <c r="B25" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="C25" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="D25" s="16">
+      <c r="C25" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D25" s="24">
         <v>296.73</v>
       </c>
-      <c r="E25" s="19">
+      <c r="E25" s="25">
         <v>68146</v>
       </c>
-      <c r="F25" s="19">
+      <c r="F25" s="25">
         <v>1424</v>
       </c>
-      <c r="G25" s="16">
+      <c r="G25" s="24">
         <v>94</v>
       </c>
-      <c r="H25" s="16">
+      <c r="H25" s="24">
         <v>21</v>
       </c>
-      <c r="I25" s="16">
+      <c r="I25" s="24">
         <v>3.16</v>
       </c>
-      <c r="J25" s="16">
+      <c r="J25" s="24">
         <v>14.13</v>
       </c>
-      <c r="K25" s="23">
+      <c r="K25" s="27">
         <v>2.09</v>
       </c>
       <c r="L25" s="21">
         <v>200</v>
       </c>
-      <c r="M25" s="26" t="s">
+      <c r="M25" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="N25" s="26" t="s">
+      <c r="N25" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="O25" s="25">
+      <c r="O25" s="15">
         <v>93.9</v>
       </c>
-      <c r="P25" s="27" t="s">
+      <c r="P25" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="Q25" s="27" t="s">
+      <c r="Q25" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="R25" s="27">
+      <c r="R25" s="29">
         <v>0</v>
       </c>
-      <c r="S25" s="28">
+      <c r="S25" s="30">
         <f t="shared" si="5"/>
         <v>21</v>
       </c>
-      <c r="T25" s="28">
+      <c r="T25" s="30">
         <f t="shared" si="6"/>
         <v>14.13</v>
       </c>
@@ -3761,65 +3784,65 @@
       </c>
     </row>
     <row r="26" ht="17" spans="1:26">
-      <c r="A26" s="14">
+      <c r="A26" s="22">
         <v>46157</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="C26" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="D26" s="16">
+      <c r="C26" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D26" s="24">
         <v>185.64</v>
       </c>
-      <c r="E26" s="19">
+      <c r="E26" s="25">
         <v>33991</v>
       </c>
-      <c r="F26" s="19">
+      <c r="F26" s="25">
         <v>646</v>
       </c>
-      <c r="G26" s="16">
+      <c r="G26" s="24">
         <v>31</v>
       </c>
-      <c r="H26" s="16">
+      <c r="H26" s="24">
         <v>12</v>
       </c>
-      <c r="I26" s="16">
+      <c r="I26" s="24">
         <v>5.99</v>
       </c>
-      <c r="J26" s="16">
+      <c r="J26" s="24">
         <v>15.47</v>
       </c>
-      <c r="K26" s="23">
+      <c r="K26" s="27">
         <v>1.9</v>
       </c>
       <c r="L26" s="21">
         <v>200</v>
       </c>
-      <c r="M26" s="26" t="s">
+      <c r="M26" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="N26" s="26" t="s">
+      <c r="N26" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="O26" s="25">
+      <c r="O26" s="15">
         <v>94.7</v>
       </c>
-      <c r="P26" s="27" t="s">
+      <c r="P26" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="Q26" s="27" t="s">
+      <c r="Q26" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="R26" s="27">
+      <c r="R26" s="29">
         <v>0</v>
       </c>
-      <c r="S26" s="28">
+      <c r="S26" s="30">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
-      <c r="T26" s="28">
+      <c r="T26" s="30">
         <f t="shared" si="6"/>
         <v>15.47</v>
       </c>
@@ -3846,65 +3869,65 @@
       </c>
     </row>
     <row r="27" spans="1:26">
-      <c r="A27" s="14">
+      <c r="A27" s="22">
         <v>46157</v>
       </c>
       <c r="B27" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="C27" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="D27" s="16">
+      <c r="D27" s="24">
         <v>249.84</v>
       </c>
-      <c r="E27" s="19">
+      <c r="E27" s="25">
         <v>31976</v>
       </c>
-      <c r="F27" s="19">
+      <c r="F27" s="25">
         <v>1097</v>
       </c>
-      <c r="G27" s="16">
+      <c r="G27" s="24">
         <v>68</v>
       </c>
-      <c r="H27" s="16">
+      <c r="H27" s="24">
         <v>18</v>
       </c>
-      <c r="I27" s="16">
+      <c r="I27" s="24">
         <v>3.67</v>
       </c>
-      <c r="J27" s="16">
+      <c r="J27" s="24">
         <v>13.88</v>
       </c>
-      <c r="K27" s="23">
+      <c r="K27" s="27">
         <v>3.43</v>
       </c>
       <c r="L27" s="21">
         <v>200</v>
       </c>
-      <c r="M27" s="26" t="s">
+      <c r="M27" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="N27" s="26" t="s">
+      <c r="N27" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="O27" s="25">
+      <c r="O27" s="15">
         <v>99.2</v>
       </c>
-      <c r="P27" s="27" t="s">
+      <c r="P27" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="Q27" s="27" t="s">
+      <c r="Q27" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="R27" s="27">
+      <c r="R27" s="29">
         <v>0</v>
       </c>
-      <c r="S27" s="28">
+      <c r="S27" s="30">
         <f t="shared" si="5"/>
         <v>18</v>
       </c>
-      <c r="T27" s="28">
+      <c r="T27" s="30">
         <f t="shared" si="6"/>
         <v>13.88</v>
       </c>
@@ -3931,65 +3954,65 @@
       </c>
     </row>
     <row r="28" spans="1:26">
-      <c r="A28" s="14">
+      <c r="A28" s="22">
         <v>46157</v>
       </c>
       <c r="B28" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="D28" s="16">
+      <c r="D28" s="24">
         <v>1470.56</v>
       </c>
-      <c r="E28" s="19">
+      <c r="E28" s="25">
         <v>434156</v>
       </c>
-      <c r="F28" s="19">
+      <c r="F28" s="25">
         <v>9378</v>
       </c>
-      <c r="G28" s="16">
+      <c r="G28" s="24">
         <v>422</v>
       </c>
-      <c r="H28" s="16">
+      <c r="H28" s="24">
         <v>101</v>
       </c>
-      <c r="I28" s="16">
+      <c r="I28" s="24">
         <v>3.48</v>
       </c>
-      <c r="J28" s="16">
+      <c r="J28" s="24">
         <v>14.56</v>
       </c>
-      <c r="K28" s="23">
+      <c r="K28" s="27">
         <v>2.16</v>
       </c>
       <c r="L28" s="21">
         <v>200</v>
       </c>
-      <c r="M28" s="26" t="s">
+      <c r="M28" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="N28" s="26" t="s">
+      <c r="N28" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="O28" s="25">
+      <c r="O28" s="15">
         <v>94.1</v>
       </c>
-      <c r="P28" s="27" t="s">
+      <c r="P28" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="Q28" s="27" t="s">
+      <c r="Q28" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="R28" s="27">
+      <c r="R28" s="29">
         <v>0</v>
       </c>
-      <c r="S28" s="28">
+      <c r="S28" s="30">
         <f t="shared" si="5"/>
         <v>101</v>
       </c>
-      <c r="T28" s="28">
+      <c r="T28" s="30">
         <f t="shared" si="6"/>
         <v>14.56</v>
       </c>
@@ -4016,65 +4039,65 @@
       </c>
     </row>
     <row r="29" spans="1:26">
-      <c r="A29" s="14">
+      <c r="A29" s="22">
         <v>46157</v>
       </c>
       <c r="B29" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="C29" s="15" t="s">
+      <c r="C29" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="D29" s="16">
+      <c r="D29" s="24">
         <v>291.96</v>
       </c>
-      <c r="E29" s="19">
+      <c r="E29" s="25">
         <v>90532</v>
       </c>
-      <c r="F29" s="19">
+      <c r="F29" s="25">
         <v>2182</v>
       </c>
-      <c r="G29" s="16">
+      <c r="G29" s="24">
         <v>96</v>
       </c>
-      <c r="H29" s="16">
+      <c r="H29" s="24">
         <v>18</v>
       </c>
-      <c r="I29" s="16">
+      <c r="I29" s="24">
         <v>3.04</v>
       </c>
-      <c r="J29" s="16">
+      <c r="J29" s="24">
         <v>16.22</v>
       </c>
-      <c r="K29" s="23">
+      <c r="K29" s="27">
         <v>2.41</v>
       </c>
       <c r="L29" s="21">
         <v>200</v>
       </c>
-      <c r="M29" s="26" t="s">
+      <c r="M29" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="N29" s="26" t="s">
+      <c r="N29" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="O29" s="25">
+      <c r="O29" s="15">
         <v>97.7</v>
       </c>
-      <c r="P29" s="27" t="s">
+      <c r="P29" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="Q29" s="27" t="s">
+      <c r="Q29" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="R29" s="27">
+      <c r="R29" s="29">
         <v>0</v>
       </c>
-      <c r="S29" s="28">
+      <c r="S29" s="30">
         <f t="shared" si="5"/>
         <v>18</v>
       </c>
-      <c r="T29" s="28">
+      <c r="T29" s="30">
         <f t="shared" si="6"/>
         <v>16.22</v>
       </c>
@@ -4101,65 +4124,65 @@
       </c>
     </row>
     <row r="30" spans="1:26">
-      <c r="A30" s="14">
+      <c r="A30" s="22">
         <v>46157</v>
       </c>
       <c r="B30" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="C30" s="15" t="s">
+      <c r="C30" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="D30" s="16">
+      <c r="D30" s="24">
         <v>589.5</v>
       </c>
-      <c r="E30" s="19">
+      <c r="E30" s="25">
         <v>116758</v>
       </c>
-      <c r="F30" s="19">
+      <c r="F30" s="25">
         <v>3643</v>
       </c>
-      <c r="G30" s="16">
+      <c r="G30" s="24">
         <v>204</v>
       </c>
-      <c r="H30" s="16">
+      <c r="H30" s="24">
         <v>45</v>
       </c>
-      <c r="I30" s="16">
+      <c r="I30" s="24">
         <v>2.89</v>
       </c>
-      <c r="J30" s="16">
+      <c r="J30" s="24">
         <v>13.1</v>
       </c>
-      <c r="K30" s="23">
+      <c r="K30" s="27">
         <v>3.12</v>
       </c>
       <c r="L30" s="21">
         <v>200</v>
       </c>
-      <c r="M30" s="26" t="s">
+      <c r="M30" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="N30" s="26" t="s">
+      <c r="N30" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="O30" s="25">
+      <c r="O30" s="15">
         <v>90.2</v>
       </c>
-      <c r="P30" s="27" t="s">
+      <c r="P30" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="Q30" s="27" t="s">
+      <c r="Q30" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="R30" s="27">
+      <c r="R30" s="29">
         <v>0</v>
       </c>
-      <c r="S30" s="28">
+      <c r="S30" s="30">
         <f t="shared" si="5"/>
         <v>45</v>
       </c>
-      <c r="T30" s="28">
+      <c r="T30" s="30">
         <f t="shared" si="6"/>
         <v>13.1</v>
       </c>
@@ -4186,65 +4209,65 @@
       </c>
     </row>
     <row r="31" spans="1:26">
-      <c r="A31" s="14">
+      <c r="A31" s="22">
         <v>46157</v>
       </c>
       <c r="B31" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="C31" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="D31" s="16">
+      <c r="D31" s="24">
         <v>138.48</v>
       </c>
-      <c r="E31" s="19">
+      <c r="E31" s="25">
         <v>16090</v>
       </c>
-      <c r="F31" s="19">
+      <c r="F31" s="25">
         <v>545</v>
       </c>
-      <c r="G31" s="16">
+      <c r="G31" s="24">
         <v>36</v>
       </c>
-      <c r="H31" s="16">
+      <c r="H31" s="24">
         <v>8</v>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="24">
         <v>3.85</v>
       </c>
-      <c r="J31" s="16">
+      <c r="J31" s="24">
         <v>17.31</v>
       </c>
-      <c r="K31" s="23">
+      <c r="K31" s="27">
         <v>3.39</v>
       </c>
       <c r="L31" s="21">
         <v>200</v>
       </c>
-      <c r="M31" s="26" t="s">
+      <c r="M31" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="N31" s="26" t="s">
+      <c r="N31" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="O31" s="25">
+      <c r="O31" s="15">
         <v>97.7</v>
       </c>
-      <c r="P31" s="27" t="s">
+      <c r="P31" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="Q31" s="27" t="s">
+      <c r="Q31" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="R31" s="27">
+      <c r="R31" s="29">
         <v>0</v>
       </c>
-      <c r="S31" s="28">
+      <c r="S31" s="30">
         <f t="shared" si="5"/>
         <v>8</v>
       </c>
-      <c r="T31" s="28">
+      <c r="T31" s="30">
         <f t="shared" si="6"/>
         <v>17.31</v>
       </c>
